--- a/DataTables/DetailText/剧情/023_01谢飞燕肺气虚.xlsx
+++ b/DataTables/DetailText/剧情/023_01谢飞燕肺气虚.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD6EA22-37D2-4268-B047-CD26997B5681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9288C49F-04D8-45DE-8EFF-2F8BE476EFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19710" yWindow="4110" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -113,10 +113,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>金姨妈</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>谢飞燕</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -476,6 +472,10 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>郭妈妈</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1004,58 +1004,58 @@
   <sheetData>
     <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="I1" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="J1" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="K1" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="L1" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="P1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="R1" s="20" t="s">
         <v>49</v>
-      </c>
-      <c r="R1" s="20" t="s">
-        <v>50</v>
       </c>
       <c r="S1" s="21" t="s">
         <v>12</v>
@@ -1231,7 +1231,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1241,8 +1241,8 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>21</v>
+      <c r="C2" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
@@ -1253,7 +1253,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I2" s="1"/>
     </row>
@@ -1265,18 +1265,18 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="1"/>
     </row>
@@ -1288,7 +1288,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
@@ -1297,7 +1297,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I4" s="1"/>
     </row>
@@ -1308,8 +1308,8 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
+      <c r="C5" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>7</v>
@@ -1318,7 +1318,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" s="1"/>
     </row>
@@ -1329,8 +1329,8 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
+      <c r="C6" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>7</v>
@@ -1339,7 +1339,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I6" s="1"/>
     </row>
@@ -1351,7 +1351,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -1360,7 +1360,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1"/>
     </row>
@@ -1372,7 +1372,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>10</v>
@@ -1381,7 +1381,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1"/>
     </row>
@@ -1393,7 +1393,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
@@ -1402,7 +1402,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" s="1"/>
     </row>
